--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,229 @@
           <t>Naturvärdesinventering vid Sweco</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>121984684</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58061</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bemersberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>639788</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6650974</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Ellen Hultman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>121984712</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57838</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bemersberg, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>640066</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6650916</v>
+      </c>
+      <c r="S4" t="n">
+        <v>100</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Skuttunge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-05-28</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ellen Hultman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Johan Holmgren</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121984684</v>
       </c>
       <c r="B3" t="n">
-        <v>58061</v>
+        <v>58069</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121984712</v>
       </c>
       <c r="B4" t="n">
-        <v>57838</v>
+        <v>57846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121984684</v>
       </c>
       <c r="B3" t="n">
-        <v>58069</v>
+        <v>58073</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121984712</v>
       </c>
       <c r="B4" t="n">
-        <v>57846</v>
+        <v>57850</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>121984684</v>
       </c>
       <c r="B3" t="n">
-        <v>58073</v>
+        <v>58077</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>121984712</v>
       </c>
       <c r="B4" t="n">
-        <v>57850</v>
+        <v>57854</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121984684</v>
+        <v>121984712</v>
       </c>
       <c r="B3" t="n">
-        <v>58077</v>
+        <v>57856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,11 +821,6 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639788</v>
+        <v>640066</v>
       </c>
       <c r="R3" t="n">
-        <v>6650974</v>
+        <v>6650916</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121984712</v>
+        <v>121984684</v>
       </c>
       <c r="B4" t="n">
-        <v>57854</v>
+        <v>58079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -935,6 +930,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640066</v>
+        <v>639788</v>
       </c>
       <c r="R4" t="n">
-        <v>6650916</v>
+        <v>6650974</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121984684</v>
+        <v>121984712</v>
       </c>
       <c r="B3" t="n">
-        <v>58079</v>
+        <v>57856</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,11 +821,6 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639788</v>
+        <v>640066</v>
       </c>
       <c r="R3" t="n">
-        <v>6650974</v>
+        <v>6650916</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121984712</v>
+        <v>121984684</v>
       </c>
       <c r="B4" t="n">
-        <v>57856</v>
+        <v>58079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -935,6 +930,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640066</v>
+        <v>639788</v>
       </c>
       <c r="R4" t="n">
-        <v>6650916</v>
+        <v>6650974</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121984712</v>
+        <v>121984684</v>
       </c>
       <c r="B3" t="n">
-        <v>57856</v>
+        <v>58079</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>103055</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,6 +821,11 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,13 +833,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>640066</v>
+        <v>639788</v>
       </c>
       <c r="R3" t="n">
-        <v>6650916</v>
+        <v>6650974</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,10 +895,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121984684</v>
+        <v>121984712</v>
       </c>
       <c r="B4" t="n">
-        <v>58079</v>
+        <v>57856</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -906,21 +911,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103055</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -930,11 +935,6 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>639788</v>
+        <v>640066</v>
       </c>
       <c r="R4" t="n">
-        <v>6650974</v>
+        <v>6650916</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>

--- a/artfynd/A 36346-2019 artfynd.xlsx
+++ b/artfynd/A 36346-2019 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121984684</v>
+        <v>121984712</v>
       </c>
       <c r="B3" t="n">
-        <v>58079</v>
+        <v>57861</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103055</v>
+        <v>103018</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -821,11 +821,6 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -833,13 +828,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>639788</v>
+        <v>640066</v>
       </c>
       <c r="R3" t="n">
-        <v>6650974</v>
+        <v>6650916</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -895,10 +890,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121984712</v>
+        <v>121984684</v>
       </c>
       <c r="B4" t="n">
-        <v>57856</v>
+        <v>58084</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,21 +906,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103018</v>
+        <v>103055</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -935,6 +930,11 @@
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>640066</v>
+        <v>639788</v>
       </c>
       <c r="R4" t="n">
-        <v>6650916</v>
+        <v>6650974</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
